--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -926,7 +926,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_paired_t.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_paired_t_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -331,7 +331,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -358,7 +358,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -528,17 +528,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -587,7 +587,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -614,17 +614,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -673,7 +673,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -700,17 +700,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -786,17 +786,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -845,7 +845,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -872,17 +872,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -931,7 +931,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -958,17 +958,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1045,17 +1045,17 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1132,17 +1132,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1218,17 +1218,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1303,17 +1303,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1388,17 +1388,17 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1473,17 +1473,17 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1559,17 +1559,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1648,17 +1648,17 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1734,17 +1734,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1819,12 +1819,12 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -1907,17 +1907,17 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析出的结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -1991,17 +1991,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析出的结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2082,17 +2082,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析出的结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2173,12 +2173,12 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
@@ -2258,17 +2258,17 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -2343,12 +2343,12 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2432,12 +2432,12 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
@@ -2519,12 +2519,12 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2689,17 +2689,17 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -2776,12 +2776,12 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
@@ -2867,12 +2867,12 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
@@ -2954,17 +2954,17 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
@@ -3041,17 +3041,17 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -3128,17 +3128,17 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
@@ -3215,12 +3215,12 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
@@ -3301,17 +3301,17 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
@@ -3388,17 +3388,17 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -3473,17 +3473,17 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
@@ -3559,12 +3559,12 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
@@ -3645,17 +3645,17 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -3731,17 +3731,17 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -3817,17 +3817,17 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -3903,17 +3903,17 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -3988,17 +3988,17 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -4073,7 +4073,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -4160,17 +4160,17 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置后分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -4245,7 +4245,7 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -4332,12 +4332,12 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
@@ -4420,12 +4420,12 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
@@ -4506,17 +4506,17 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析结果提示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
@@ -4592,12 +4592,12 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
@@ -4682,17 +4682,17 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
@@ -4771,17 +4771,17 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
@@ -4861,17 +4861,17 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
@@ -4950,17 +4950,17 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
@@ -5040,17 +5040,17 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -5129,12 +5129,12 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
@@ -5217,17 +5217,17 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
@@ -5305,17 +5305,17 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
@@ -5394,17 +5394,17 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="2">
@@ -5483,12 +5483,12 @@
     <row r="63" ht="64" customHeight="1">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
@@ -5570,17 +5570,17 @@
     <row r="64" ht="64" customHeight="1">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
@@ -5657,12 +5657,12 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
@@ -5746,17 +5746,17 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="2">
@@ -5835,17 +5835,17 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="2">
@@ -5924,17 +5924,17 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="2">
@@ -6013,17 +6013,17 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="2">
@@ -6101,12 +6101,12 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
@@ -6191,17 +6191,17 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">定类变量暂不支持分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="2">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -6453,7 +6453,7 @@
     <row r="74" ht="64" customHeight="1">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_paired_t_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -331,7 +331,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -501,7 +501,7 @@
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -587,7 +587,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -673,7 +673,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -720,7 +720,7 @@
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
@@ -759,7 +759,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -806,7 +806,7 @@
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
@@ -845,7 +845,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -892,7 +892,7 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -931,7 +931,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -978,7 +978,7 @@
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="2">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="L14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="2">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="2">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="L20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M20" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="2">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="2">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M45" t="inlineStr" s="2">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="L46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M46" t="inlineStr" s="2">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="2">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="E50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="2">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="E54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="2">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="2">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
